--- a/tools/SpaceCalc.xlsx
+++ b/tools/SpaceCalc.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/Development/aerospace/prometheus_unbound/tools/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/Code/aerospace/prometheus_unbound/tools/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89624C7C-D3B6-7F4A-9956-6B2DEF4102A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31A387C-827C-F94A-9D07-D6D721AB3A61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="25600" windowHeight="14400" xr2:uid="{F4E1B1BE-E6BE-4736-BB82-C5B26D151CF6}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="25600" windowHeight="14260" activeTab="3" xr2:uid="{F4E1B1BE-E6BE-4736-BB82-C5B26D151CF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Astrodynamics" sheetId="1" r:id="rId1"/>
-    <sheet name="Propulsion" sheetId="2" r:id="rId2"/>
-    <sheet name="Thermal" sheetId="7" r:id="rId3"/>
-    <sheet name="Power" sheetId="4" r:id="rId4"/>
-    <sheet name="Artificial Gravity" sheetId="6" r:id="rId5"/>
-    <sheet name="Geometry" sheetId="5" r:id="rId6"/>
-    <sheet name="Costs" sheetId="3" r:id="rId7"/>
-    <sheet name="Payload" sheetId="8" r:id="rId8"/>
+    <sheet name="Aerodynamics" sheetId="10" r:id="rId2"/>
+    <sheet name="Propulsion" sheetId="2" r:id="rId3"/>
+    <sheet name="Thermal" sheetId="7" r:id="rId4"/>
+    <sheet name="Power" sheetId="4" r:id="rId5"/>
+    <sheet name="Artificial Gravity" sheetId="6" r:id="rId6"/>
+    <sheet name="SSTO" sheetId="8" r:id="rId7"/>
+    <sheet name="Geometry" sheetId="5" r:id="rId8"/>
+    <sheet name="Costs" sheetId="3" r:id="rId9"/>
+    <sheet name="Crew" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="469">
   <si>
     <t>Constants</t>
   </si>
@@ -63,12 +65,6 @@
     <t>V_apoapsis</t>
   </si>
   <si>
-    <t>Perigee, km</t>
-  </si>
-  <si>
-    <t>Apogee, km</t>
-  </si>
-  <si>
     <t>Transfer</t>
   </si>
   <si>
@@ -171,18 +167,6 @@
     <t>Mass, empty</t>
   </si>
   <si>
-    <t>Cell Efficiency, BOL</t>
-  </si>
-  <si>
-    <t>Cell Efficiency, EOL</t>
-  </si>
-  <si>
-    <t>Solar Irradiance</t>
-  </si>
-  <si>
-    <t>Area, m^2</t>
-  </si>
-  <si>
     <t>Shell mass,kg</t>
   </si>
   <si>
@@ -393,9 +377,6 @@
     <t>mass flow, kg/s</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>Inputs (bi-prop engine)</t>
   </si>
   <si>
@@ -477,9 +458,6 @@
     <t>Transfer Orbit</t>
   </si>
   <si>
-    <t>Hohmann Manouever (LEO-GEO)</t>
-  </si>
-  <si>
     <t>Venus</t>
   </si>
   <si>
@@ -522,42 +500,18 @@
     <t>total modules</t>
   </si>
   <si>
-    <t>total cost, co</t>
-  </si>
-  <si>
-    <t>total month available</t>
-  </si>
-  <si>
-    <t>total moths, construction</t>
-  </si>
-  <si>
     <t>total months, leop</t>
   </si>
   <si>
-    <t>total month, non-operational</t>
-  </si>
-  <si>
     <t>utilization</t>
   </si>
   <si>
-    <t>total month, revenue generatting</t>
-  </si>
-  <si>
-    <t>gross profit need</t>
-  </si>
-  <si>
     <t>per month, M</t>
   </si>
   <si>
-    <t>per man-month</t>
-  </si>
-  <si>
     <t>per man-day</t>
   </si>
   <si>
-    <t>7day</t>
-  </si>
-  <si>
     <t>total ppl needed</t>
   </si>
   <si>
@@ -738,66 +692,6 @@
     <t>Electric Propulsion calculation</t>
   </si>
   <si>
-    <t>Total Power, W</t>
-  </si>
-  <si>
-    <t>Total Power, daily, W-h</t>
-  </si>
-  <si>
-    <t>Total P</t>
-  </si>
-  <si>
-    <t>Orbital parameters</t>
-  </si>
-  <si>
-    <t>Power Parameters</t>
-  </si>
-  <si>
-    <t>Eccentricty</t>
-  </si>
-  <si>
-    <t>dOmega</t>
-  </si>
-  <si>
-    <t>dG</t>
-  </si>
-  <si>
-    <t>Semimajor axis</t>
-  </si>
-  <si>
-    <t>R_Earth, m</t>
-  </si>
-  <si>
-    <t>Beta_min</t>
-  </si>
-  <si>
-    <t>Ecliptic_obliquity</t>
-  </si>
-  <si>
-    <t>Intermediate_values</t>
-  </si>
-  <si>
-    <t>cosGsinOmega</t>
-  </si>
-  <si>
-    <t>sinGcosOmega</t>
-  </si>
-  <si>
-    <t>Beta_angle</t>
-  </si>
-  <si>
-    <t>sinG</t>
-  </si>
-  <si>
-    <t>rad_to_deg</t>
-  </si>
-  <si>
-    <t>entry_deg</t>
-  </si>
-  <si>
-    <t>Illuminated</t>
-  </si>
-  <si>
     <t>Interplanetary Manoeuver (Earth-Mars)</t>
   </si>
   <si>
@@ -819,19 +713,754 @@
     <t>Sphere radius, km</t>
   </si>
   <si>
-    <t>Fusion</t>
-  </si>
-  <si>
     <t>In MW</t>
   </si>
   <si>
     <t>Moon</t>
   </si>
   <si>
-    <t>Origin(Moon)</t>
-  </si>
-  <si>
     <t>Total deltaV</t>
+  </si>
+  <si>
+    <t>P_sun</t>
+  </si>
+  <si>
+    <t>Irradiation, high, W/m^2</t>
+  </si>
+  <si>
+    <t>Irradiation, low, W/m^2</t>
+  </si>
+  <si>
+    <t>Distance, periapsis, m</t>
+  </si>
+  <si>
+    <t>Distance, apoapsis, m</t>
+  </si>
+  <si>
+    <t>Sphere area, periapsis</t>
+  </si>
+  <si>
+    <t>Sphere area, apoapsis</t>
+  </si>
+  <si>
+    <t>Tau</t>
+  </si>
+  <si>
+    <t>Opacity</t>
+  </si>
+  <si>
+    <t>Environment parameters</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
+    <t>Capacity factor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Sol duration</t>
+    </r>
+  </si>
+  <si>
+    <t>Energy per sol, high, w-h</t>
+  </si>
+  <si>
+    <t>Daytime fraction</t>
+  </si>
+  <si>
+    <t>Solar Panel details A</t>
+  </si>
+  <si>
+    <t>Energy per sol, low, w-h</t>
+  </si>
+  <si>
+    <t>Irradiation, NASA nominal</t>
+  </si>
+  <si>
+    <t>Energy per sol, median, w-h</t>
+  </si>
+  <si>
+    <t>Power/m^2, median</t>
+  </si>
+  <si>
+    <t>total months available</t>
+  </si>
+  <si>
+    <t>7-day stay for 1 person</t>
+  </si>
+  <si>
+    <t>total months, construction</t>
+  </si>
+  <si>
+    <t>total months, revenue generatting</t>
+  </si>
+  <si>
+    <t>gross profit needed, M</t>
+  </si>
+  <si>
+    <t>per man-month, M</t>
+  </si>
+  <si>
+    <t>total months, non-operational</t>
+  </si>
+  <si>
+    <t>Origin(Earth)</t>
+  </si>
+  <si>
+    <t>kW/m^2</t>
+  </si>
+  <si>
+    <t>Radiator area</t>
+  </si>
+  <si>
+    <t>Radiator T, K</t>
+  </si>
+  <si>
+    <t>Environment T, K</t>
+  </si>
+  <si>
+    <t>Power Balance, W/m^2</t>
+  </si>
+  <si>
+    <t>MW/m^2</t>
+  </si>
+  <si>
+    <t>As square, m</t>
+  </si>
+  <si>
+    <t>A circle</t>
+  </si>
+  <si>
+    <t>Hohmann Manouever</t>
+  </si>
+  <si>
+    <t>light-second</t>
+  </si>
+  <si>
+    <t>Distances, m</t>
+  </si>
+  <si>
+    <t>light-minute</t>
+  </si>
+  <si>
+    <t>light-hour</t>
+  </si>
+  <si>
+    <t>light-day</t>
+  </si>
+  <si>
+    <t>light-year</t>
+  </si>
+  <si>
+    <t>au</t>
+  </si>
+  <si>
+    <t>parsec</t>
+  </si>
+  <si>
+    <t>E, J</t>
+  </si>
+  <si>
+    <t>Relativistic Kinetic Energy</t>
+  </si>
+  <si>
+    <t>Exhaust velocity, m/s</t>
+  </si>
+  <si>
+    <t>m ,kg</t>
+  </si>
+  <si>
+    <t>MT, TNT</t>
+  </si>
+  <si>
+    <t>Fusion Drive</t>
+  </si>
+  <si>
+    <t>Speed of Light</t>
+  </si>
+  <si>
+    <t>Turbojet propulstion</t>
+  </si>
+  <si>
+    <t>Waste Heat Radiatior Efficiency</t>
+  </si>
+  <si>
+    <t>Intake pressue, Pa</t>
+  </si>
+  <si>
+    <t>Intake temperature, K</t>
+  </si>
+  <si>
+    <t>Intake loss</t>
+  </si>
+  <si>
+    <t>Compressor Ratio</t>
+  </si>
+  <si>
+    <t>Compressor Efficiency</t>
+  </si>
+  <si>
+    <t>Turbine Entry Temp, K</t>
+  </si>
+  <si>
+    <t>Turbine pressure loss</t>
+  </si>
+  <si>
+    <t>Turbine efficiency</t>
+  </si>
+  <si>
+    <t>Nozzle loss</t>
+  </si>
+  <si>
+    <t>Outpus</t>
+  </si>
+  <si>
+    <t>gamma_a</t>
+  </si>
+  <si>
+    <t>Intermediates</t>
+  </si>
+  <si>
+    <t>T_out</t>
+  </si>
+  <si>
+    <t>T_out_is</t>
+  </si>
+  <si>
+    <t>P_out</t>
+  </si>
+  <si>
+    <t>cp_a</t>
+  </si>
+  <si>
+    <t>Q_in, J</t>
+  </si>
+  <si>
+    <t>Fuel flow, kg/s</t>
+  </si>
+  <si>
+    <t>Air mass flow, kg/s</t>
+  </si>
+  <si>
+    <t>P_out_cmb</t>
+  </si>
+  <si>
+    <t>Combustor loss</t>
+  </si>
+  <si>
+    <t>gamma_t</t>
+  </si>
+  <si>
+    <t>cp_t</t>
+  </si>
+  <si>
+    <t>cp_b</t>
+  </si>
+  <si>
+    <t>work_in</t>
+  </si>
+  <si>
+    <t>npr</t>
+  </si>
+  <si>
+    <t>npr_adj</t>
+  </si>
+  <si>
+    <t>gamma_out</t>
+  </si>
+  <si>
+    <t>t_nozz</t>
+  </si>
+  <si>
+    <t>density</t>
+  </si>
+  <si>
+    <t>p_nozz</t>
+  </si>
+  <si>
+    <t>mach_no</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>Fuel burn, kg/hr</t>
+  </si>
+  <si>
+    <t>SPFC, kg -kN/s</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>Escape velocity</t>
+  </si>
+  <si>
+    <t>Derived values</t>
+  </si>
+  <si>
+    <t>Orbital speed</t>
+  </si>
+  <si>
+    <t>aero loss</t>
+  </si>
+  <si>
+    <t>Orbital speed, adj</t>
+  </si>
+  <si>
+    <t>Ballistic flight</t>
+  </si>
+  <si>
+    <t>Launch speed</t>
+  </si>
+  <si>
+    <t>Re-entry</t>
+  </si>
+  <si>
+    <t>Margins</t>
+  </si>
+  <si>
+    <t>"Two-thirds"</t>
+  </si>
+  <si>
+    <t>Max two-way trip</t>
+  </si>
+  <si>
+    <t>Ferry</t>
+  </si>
+  <si>
+    <t>Sabatier reaction requirements</t>
+  </si>
+  <si>
+    <t>Energy per ton-day, w-h</t>
+  </si>
+  <si>
+    <t>Area required, m^2</t>
+  </si>
+  <si>
+    <t>Nominal power</t>
+  </si>
+  <si>
+    <t>Tonnes per day</t>
+  </si>
+  <si>
+    <t>Area required, sq. km</t>
+  </si>
+  <si>
+    <t>Nominal power, MW</t>
+  </si>
+  <si>
+    <t>Per day, kW-h</t>
+  </si>
+  <si>
+    <t>Tons per day</t>
+  </si>
+  <si>
+    <t>Array mass, tonnes/sq km</t>
+  </si>
+  <si>
+    <t>Mass of reactor, tonnes</t>
+  </si>
+  <si>
+    <t>Nominal electric power, kW</t>
+  </si>
+  <si>
+    <t>Belgica</t>
+  </si>
+  <si>
+    <t>Expedition Name</t>
+  </si>
+  <si>
+    <t>Crew Size</t>
+  </si>
+  <si>
+    <t>Start Date</t>
+  </si>
+  <si>
+    <t>End Date</t>
+  </si>
+  <si>
+    <t>Casualties</t>
+  </si>
+  <si>
+    <t>Length, months</t>
+  </si>
+  <si>
+    <t>Southern Cross</t>
+  </si>
+  <si>
+    <t>Discovery</t>
+  </si>
+  <si>
+    <t>Gauss Expedition</t>
+  </si>
+  <si>
+    <t>Swedish Expedition</t>
+  </si>
+  <si>
+    <t>Scottish Expedition</t>
+  </si>
+  <si>
+    <t>Nimrod Expedition</t>
+  </si>
+  <si>
+    <t>Japanese Expedition</t>
+  </si>
+  <si>
+    <t>Norway South Pole</t>
+  </si>
+  <si>
+    <t>Terra Nova</t>
+  </si>
+  <si>
+    <t>Second German</t>
+  </si>
+  <si>
+    <t>Australasian Expedition</t>
+  </si>
+  <si>
+    <t>Imperial trans-antarctic</t>
+  </si>
+  <si>
+    <t>Shackleton-Rowett</t>
+  </si>
+  <si>
+    <t>Means</t>
+  </si>
+  <si>
+    <t>Casualty Rate</t>
+  </si>
+  <si>
+    <t>Wing loading</t>
+  </si>
+  <si>
+    <t>Wing area, m^2</t>
+  </si>
+  <si>
+    <t>Aerodynamic flight</t>
+  </si>
+  <si>
+    <t>CL</t>
+  </si>
+  <si>
+    <t>CD</t>
+  </si>
+  <si>
+    <t>density, kg/m^3</t>
+  </si>
+  <si>
+    <t>Deg latitude</t>
+  </si>
+  <si>
+    <t>20 deg lat</t>
+  </si>
+  <si>
+    <t>Deg lon at lat:</t>
+  </si>
+  <si>
+    <t>30 deg lon</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>Two-way, at 45 deg</t>
+  </si>
+  <si>
+    <t>One-way, at 45 deg</t>
+  </si>
+  <si>
+    <t>ISS Power needs</t>
+  </si>
+  <si>
+    <t>Annual, kw-h</t>
+  </si>
+  <si>
+    <t>Daily, kw-h</t>
+  </si>
+  <si>
+    <t>Load, average</t>
+  </si>
+  <si>
+    <t>Load, peak</t>
+  </si>
+  <si>
+    <t>Power, peak</t>
+  </si>
+  <si>
+    <t>Power, average low</t>
+  </si>
+  <si>
+    <t>Per-person</t>
+  </si>
+  <si>
+    <t>Martian base, industrial</t>
+  </si>
+  <si>
+    <t>Martian base, life support</t>
+  </si>
+  <si>
+    <t>With Nuclear Power</t>
+  </si>
+  <si>
+    <t>Power peak, kW</t>
+  </si>
+  <si>
+    <t>Area required, meters^2</t>
+  </si>
+  <si>
+    <t>Power, average high</t>
+  </si>
+  <si>
+    <t>Number of people</t>
+  </si>
+  <si>
+    <t>g, Earth</t>
+  </si>
+  <si>
+    <t>Mass, kg</t>
+  </si>
+  <si>
+    <t>Weight, Earth</t>
+  </si>
+  <si>
+    <t>Weight, Mars</t>
+  </si>
+  <si>
+    <t>g, Mars</t>
+  </si>
+  <si>
+    <t>Density, Earth</t>
+  </si>
+  <si>
+    <t>Density, Mars</t>
+  </si>
+  <si>
+    <t>Lift at stall, Earth</t>
+  </si>
+  <si>
+    <t>Drag at stall, Earth</t>
+  </si>
+  <si>
+    <t>Lift at stall, Mars</t>
+  </si>
+  <si>
+    <t>Drag at stall, Mars</t>
+  </si>
+  <si>
+    <t>Stall velocity, knots</t>
+  </si>
+  <si>
+    <t>Stall velocity, m/s</t>
+  </si>
+  <si>
+    <t>Thrust at stall, N</t>
+  </si>
+  <si>
+    <t>Thrust for takeoff</t>
+  </si>
+  <si>
+    <t>Thrust at stall, kN</t>
+  </si>
+  <si>
+    <t>Throttle low, %</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>Hill Sphere, au</t>
+  </si>
+  <si>
+    <t>Mean Anom.</t>
+  </si>
+  <si>
+    <t>Eccen. Anom</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>ve</t>
+  </si>
+  <si>
+    <t>Total mass, t</t>
+  </si>
+  <si>
+    <t>Total mass, tonnes</t>
+  </si>
+  <si>
+    <t>Mass,tonnes</t>
+  </si>
+  <si>
+    <t>Solar Panel details B</t>
+  </si>
+  <si>
+    <t>Orbital  power w/m^2</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>B23</t>
+  </si>
+  <si>
+    <t>B24</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>B26</t>
+  </si>
+  <si>
+    <t>B27</t>
+  </si>
+  <si>
+    <t>B28</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>E15</t>
+  </si>
+  <si>
+    <t>E16</t>
+  </si>
+  <si>
+    <t>E17</t>
+  </si>
+  <si>
+    <t>E18</t>
+  </si>
+  <si>
+    <t>E19</t>
+  </si>
+  <si>
+    <t>E21</t>
+  </si>
+  <si>
+    <t>E22</t>
+  </si>
+  <si>
+    <t>E23</t>
+  </si>
+  <si>
+    <t>E24</t>
+  </si>
+  <si>
+    <t>E25</t>
+  </si>
+  <si>
+    <t>Tag</t>
+  </si>
+  <si>
+    <t>V_orbital</t>
+  </si>
+  <si>
+    <t>E_total, J/kg</t>
+  </si>
+  <si>
+    <t>Perigee alt, km</t>
+  </si>
+  <si>
+    <t>Apogee alt, km</t>
   </si>
 </sst>
 </file>
@@ -847,9 +1476,9 @@
     <numFmt numFmtId="169" formatCode="0.00000000"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="0.0000%"/>
-    <numFmt numFmtId="172" formatCode="0.000000000000000"/>
+    <numFmt numFmtId="172" formatCode="[$-1009]d/mmm/yy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -921,8 +1550,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -953,6 +1596,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -967,7 +1616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1002,7 +1651,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1015,7 +1663,14 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1023,6 +1678,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1035,6 +1696,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1352,7 +2016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FF034C1-A996-4CD3-9FFB-54EC88DD8700}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
@@ -1370,47 +2034,47 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="F1" s="32" t="s">
-        <v>144</v>
-      </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
+        <v>134</v>
+      </c>
+      <c r="F1" s="38" t="s">
+        <v>261</v>
+      </c>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B2" s="5">
         <v>1.32712440018E+20</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D2">
         <v>696340000</v>
       </c>
       <c r="E2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G2" s="10" t="s">
         <v>1</v>
@@ -1419,18 +2083,18 @@
         <v>2</v>
       </c>
       <c r="I2" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" s="10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="K2" s="10" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B3" s="2">
         <v>398600441800000</v>
@@ -1446,29 +2110,29 @@
         <v>29784.479863882669</v>
       </c>
       <c r="F3" t="s">
-        <v>6</v>
+        <v>467</v>
       </c>
       <c r="G3">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H3">
-        <v>35786</v>
+        <v>17032</v>
       </c>
       <c r="I3">
         <f>G3</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="J3" s="3">
-        <f>I15-G15</f>
-        <v>2440.0839758003485</v>
+        <f>ABS(I15-G15)</f>
+        <v>1025.9128809974386</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B4" s="5">
         <v>42828370000000</v>
@@ -1484,29 +2148,29 @@
         <v>24131.463116555489</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>468</v>
       </c>
       <c r="G4">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H4">
-        <v>35786</v>
+        <v>17032</v>
       </c>
       <c r="I4">
         <f>H4</f>
-        <v>35786</v>
+        <v>17032</v>
       </c>
       <c r="J4" s="3">
-        <f>H16-I16</f>
-        <v>1472.0341736129992</v>
+        <f>ABS(H16-I16)</f>
+        <v>646.43719948848047</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B5" s="5">
         <v>324859000000000</v>
@@ -1515,31 +2179,31 @@
         <v>108210000000</v>
       </c>
       <c r="F5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <f>G3*1000+D3</f>
-        <v>6628137</v>
+        <f>G3*1000+D4</f>
+        <v>3696000</v>
       </c>
       <c r="H5">
-        <f>H3*1000+D3</f>
-        <v>42164137</v>
+        <f>H3*1000+D4</f>
+        <v>20428000</v>
       </c>
       <c r="I5">
-        <f>I3*1000+D3</f>
-        <v>6628137</v>
+        <f>I3*1000+D4</f>
+        <v>3696000</v>
       </c>
       <c r="J5" s="3">
         <f>SQRT(I16^2+H16^2-2*H16*I16*COS(RADIANS(I8)))</f>
-        <v>1472.0341736129997</v>
+        <v>646.67364842125971</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B6" s="5">
         <v>1.26686534E+17</v>
@@ -1548,31 +2212,31 @@
         <v>778479000000</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <f>G4*1000+D3</f>
-        <v>6628137</v>
+        <f>G4*1000+D4</f>
+        <v>3696000</v>
       </c>
       <c r="H6">
-        <f>H4*1000+D3</f>
-        <v>42164137</v>
+        <f>H4*1000+D4</f>
+        <v>20428000</v>
       </c>
       <c r="I6">
-        <f>I4*1000+D3</f>
-        <v>42164137</v>
+        <f>I4*1000+D4</f>
+        <v>20428000</v>
       </c>
       <c r="J6" s="3">
         <f>J3+MAX(J4,J5)</f>
-        <v>3912.118149413348</v>
+        <v>1672.5865294186983</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="B7" s="5">
         <v>3.7931187E+16</v>
@@ -1590,352 +2254,419 @@
       </c>
       <c r="I7">
         <f>(I6-I5)/(I6+I5)</f>
-        <v>0.72831202743286771</v>
+        <v>0.69358315370585311</v>
       </c>
       <c r="J7" s="4" t="str">
         <f xml:space="preserve"> IF(H10/G10&gt;11.94, "Yes","No")</f>
         <v>No</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B8" s="5">
         <v>5793939000000000</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G8">
         <v>0</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="I8">
         <f>G8-H8</f>
-        <v>0</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B9" s="5">
         <v>6836529000000000</v>
       </c>
+      <c r="F9" t="s">
+        <v>465</v>
+      </c>
+      <c r="G9">
+        <f>SQRT(B4/G10)</f>
+        <v>3404.0802643133206</v>
+      </c>
+      <c r="H9">
+        <f>SQRT(B4/H10)</f>
+        <v>1447.947609957864</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>223</v>
       </c>
       <c r="B10" s="2">
         <f>B3/81.30057</f>
         <v>4902800088609.4648</v>
       </c>
-      <c r="D10">
-        <v>1737400</v>
-      </c>
       <c r="F10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G10">
         <f>(G5+G6)/2</f>
-        <v>6628137</v>
+        <v>3696000</v>
       </c>
       <c r="H10">
         <f>(H5+H6)/2</f>
-        <v>42164137</v>
+        <v>20428000</v>
       </c>
       <c r="I10">
         <f>(I5+I6)/2</f>
-        <v>24396137</v>
+        <v>12062000</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="32" t="s">
-        <v>142</v>
-      </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="D11" s="32"/>
+      <c r="A11" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="38"/>
+      <c r="C11" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="F11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G11" s="3">
-        <f>2*PI()*SQRT(G10^3/B3)/60</f>
-        <v>89.504927438556066</v>
+        <f>2*PI()*SQRT(G10^3/B4)/60</f>
+        <v>113.7000848598786</v>
       </c>
       <c r="H11" s="3">
-        <f>2*PI()*SQRT(H10^3/B3)/60</f>
-        <v>1436.0665082861817</v>
+        <f>2*PI()*SQRT(H10^3/B4)/60</f>
+        <v>1477.4119884397353</v>
       </c>
       <c r="I11" s="3">
-        <f>2*PI()*SQRT(I10^3/B3)/60</f>
-        <v>632.03528622981901</v>
+        <f>2*PI()*SQRT(I10^3/B4)/60</f>
+        <v>670.33490049049362</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5">
         <v>1.08262668E-3</v>
       </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="11">
-        <f>C5</f>
-        <v>108210000000</v>
+      <c r="C12">
+        <v>104</v>
+      </c>
+      <c r="D12" s="6">
+        <f>RADIANS(C12)-C14*SIN(RADIANS(C12))</f>
+        <v>1.7245627467010549</v>
       </c>
       <c r="F12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G12" s="3">
-        <f>((-3/2)*D3^2/((G10*(1-G7^2))^2)*B12*(2*PI()/(G11*60))*COS(RADIANS(G8)))*B13*B14</f>
-        <v>-8.7094908387929912</v>
+        <f>((-3/2)*D4^2/((G10*(1-G7^2))^2)*B12*(2*PI()/(G11*60))*COS(RADIANS(G8)))*B13*B14</f>
+        <v>-6.4131984486937359</v>
       </c>
       <c r="H12" s="6">
-        <f>((-3/2)*D3^2/((H10*(1-H7^2))^2)*B12*(2*PI()/(H11*60))*COS(RADIANS(H8)))*B13*B14</f>
-        <v>-1.341410430880031E-2</v>
+        <f>((-3/2)*D4^2/((H10*(1-H7^2))^2)*B12*(2*PI()/(H11*60))*COS(RADIANS(H8)))*B13*B14</f>
+        <v>-1.6154326738841037E-2</v>
       </c>
       <c r="I12" s="6">
-        <f>((-3/2)*D3^2/((I10*(1-I7^2))^2)*B12*(2*PI()/(I11*60))*COS(RADIANS(I8)))*B13*B14</f>
-        <v>-0.41290874566633368</v>
+        <f>((-3/2)*D4^2/((I10*(1-I7^2))^2)*B12*(2*PI()/(I11*60))*COS(RADIANS(I8)))*B13*B14</f>
+        <v>-0.37920440483774581</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13">
-        <v>86400</v>
-      </c>
-      <c r="C13" t="s">
-        <v>74</v>
-      </c>
-      <c r="D13" s="3">
-        <f>D12/B15</f>
-        <v>0.72332887700534765</v>
+        <v>145</v>
+      </c>
+      <c r="B13" s="20">
+        <v>88642.663</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D13">
+        <f>DEGREES(D12)</f>
+        <v>98.810166891459275</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G13">
         <f>B13/(G11*60)</f>
-        <v>16.088499719622035</v>
+        <v>12.993637766298534</v>
       </c>
       <c r="H13">
         <f>B13/(H11*60)</f>
-        <v>1.0027390734977257</v>
+        <v>0.99997680283269885</v>
       </c>
       <c r="I13">
         <f>B13/(I11*60)</f>
-        <v>2.2783538061455495</v>
+        <v>2.2039397256291569</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B14">
         <f>180/PI()</f>
         <v>57.295779513082323</v>
       </c>
-      <c r="C14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14">
-        <v>6.7200000000000003E-3</v>
+      <c r="C14" s="6">
+        <v>9.3352647981552503E-2</v>
       </c>
       <c r="F14" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2">
-        <f>SQRT(2*B3)*SQRT((G5*G6)/(G5+G6))</f>
-        <v>51400178370.419357</v>
+        <f>SQRT(2*B4)*SQRT((G5*G6)/(G5+G6))</f>
+        <v>12581480656.902033</v>
       </c>
       <c r="H14" s="2">
-        <f>SQRT(2*B3)*SQRT((H5*H6)/(H5+H6))</f>
-        <v>129640439818.42905</v>
+        <f>SQRT(2*B4)*SQRT((H5*H6)/(H5+H6))</f>
+        <v>29578673776.219246</v>
       </c>
       <c r="I14" s="2">
-        <f>SQRT(2*B3)*SQRT((I5*I6)/(I5+I6))</f>
-        <v>67573389253.528755</v>
+        <f>SQRT(2*B4)*SQRT((I5*I6)/(I5+I6))</f>
+        <v>16373254665.068565</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="B15" s="5">
         <v>149600000000</v>
       </c>
-      <c r="C15" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="3">
-        <f>(2*PI()*SQRT(D12^3/B2)/(3600*24))/365.25</f>
-        <v>0.61520687455425493</v>
-      </c>
       <c r="F15" t="s">
         <v>4</v>
       </c>
       <c r="G15" s="3">
         <f>G14/G5</f>
-        <v>7754.8454973726939</v>
+        <v>3404.0802643133206</v>
       </c>
       <c r="H15" s="3">
         <f>H14/H5</f>
-        <v>3074.6612890103511</v>
+        <v>1447.947609957864</v>
       </c>
       <c r="I15" s="3">
         <f>I14/I5</f>
-        <v>10194.929473173042</v>
+        <v>4429.9931453107592</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="C16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" s="12">
-        <f>D13*(1+D14)</f>
-        <v>0.72818964705882361</v>
+      <c r="A16" t="s">
+        <v>407</v>
+      </c>
+      <c r="B16" s="5">
+        <v>6.6742999999999994E-11</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
       </c>
       <c r="G16" s="3">
         <f>G14/G6</f>
-        <v>7754.8454973726939</v>
+        <v>3404.0802643133206</v>
       </c>
       <c r="H16" s="3">
         <f>H14/H6</f>
-        <v>3074.6612890103511</v>
+        <v>1447.947609957864</v>
       </c>
       <c r="I16" s="3">
         <f>I14/I6</f>
-        <v>1602.6271153973519</v>
-      </c>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C17" t="s">
-        <v>152</v>
-      </c>
-      <c r="D17" s="12">
-        <f>D13*(1-D14)</f>
-        <v>0.7184681069518718</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="F18" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="F19" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32" t="s">
-        <v>143</v>
-      </c>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32" t="s">
-        <v>140</v>
-      </c>
-      <c r="K19" s="32"/>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.2">
+        <v>801.51041046938349</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="38" t="s">
+        <v>142</v>
+      </c>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38" t="s">
+        <v>408</v>
+      </c>
+      <c r="D17" s="38"/>
+      <c r="F17" t="s">
+        <v>466</v>
+      </c>
+      <c r="G17" s="5">
+        <f>9.8065*G3*1000+(G15^2)/2</f>
+        <v>8735831.2229437232</v>
+      </c>
+      <c r="H17" s="5">
+        <f>9.8065*H3*1000+(H15^2)/2</f>
+        <v>168072584.14059135</v>
+      </c>
+      <c r="I17" s="5">
+        <f>SQRT(H17/G17)</f>
+        <v>4.3862796941896764</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" s="11">
+        <f>C3*B19</f>
+        <v>5906507200000</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="6">
+        <f>(C3*(1-0.016)*POWER((B3/B16)/(3*(B2/B16+B3/B16)),1/3))/B15</f>
+        <v>9.8438040316678084E-3</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="3">
+        <v>39.481999999999999</v>
+      </c>
+      <c r="C19" t="s">
+        <v>121</v>
+      </c>
+      <c r="D19" s="6">
+        <f>(C3*(1-0.0934)*POWER((B4/B16)/(3*(B2/B16+B4/B16)),1/3))/B15</f>
+        <v>4.3117001775866137E-3</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>252</v>
+      </c>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38" t="s">
+        <v>136</v>
+      </c>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="K19" s="38"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20">
+        <v>0.24879999999999999</v>
+      </c>
       <c r="F20" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="G20" s="3">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="H20" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="I20" s="5">
         <f>C3</f>
         <v>149600000000</v>
       </c>
       <c r="J20" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="K20" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="3">
+        <f>(2*PI()*SQRT(B18^3/B2)/(3600*24))/365.25</f>
+        <v>248.09395974473102</v>
+      </c>
       <c r="F21" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G21" s="3">
-        <f>G20*1000+D10</f>
-        <v>1837400</v>
+        <f>G20*1000+D3</f>
+        <v>6628137</v>
       </c>
       <c r="H21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="I21" s="5">
         <f>C4</f>
         <v>227900000000</v>
       </c>
       <c r="J21" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K21" s="3">
-        <v>36000</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="12">
+        <f>B19*(1+B20)</f>
+        <v>49.305121599999993</v>
+      </c>
       <c r="C22" s="5"/>
       <c r="F22" t="s">
         <v>4</v>
       </c>
       <c r="G22" s="3">
-        <f>SQRT(B10/G21)</f>
-        <v>1633.50412915419</v>
+        <f>SQRT(B3/G21)</f>
+        <v>7754.8454973726948</v>
       </c>
       <c r="H22" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I22" s="5">
         <f>SQRT(2*B2)*SQRT((I20*I21)/(I20+I21))</f>
         <v>4896100189417301</v>
       </c>
       <c r="J22" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K22" s="3">
         <f>K20*1000+D4</f>
-        <v>3696000</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.2">
+        <v>3496000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>144</v>
+      </c>
+      <c r="B23" s="12">
+        <f>B19*(1-B20)</f>
+        <v>29.658878399999999</v>
+      </c>
       <c r="C23" s="5"/>
       <c r="E23" s="3"/>
       <c r="F23" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="G23" s="3">
         <f>SQRT(2)*G22</f>
-        <v>2310.1236936423074</v>
+        <v>10967.007676492396</v>
       </c>
       <c r="H23" t="s">
         <v>4</v>
@@ -1945,16 +2676,16 @@
         <v>32727.942442629017</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K23" s="3">
         <f>K21*1000+D4</f>
-        <v>39396000</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.2">
+        <v>53396000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="F24" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="G24" s="3">
         <f>I23-E3</f>
@@ -1972,112 +2703,789 @@
       </c>
       <c r="K24" s="6">
         <f>(K23-K22)/(K23+K22)</f>
-        <v>0.82846003898635479</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.2">
+        <v>0.8771004710679885</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="38" t="s">
+        <v>263</v>
+      </c>
+      <c r="B25" s="38"/>
+      <c r="C25" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D25" s="1"/>
       <c r="F25" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G25" s="3">
         <f>SQRT(G23^2+G24^2)</f>
-        <v>3741.7433680582208</v>
+        <v>11355.141096821442</v>
       </c>
       <c r="J25" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K25" s="3">
         <f>SQRT(B4*(1+K24)/K22)</f>
-        <v>4603.0164646209969</v>
-      </c>
-    </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.2">
-      <c r="E26">
-        <f>676+145+93+388+673</f>
-        <v>1975</v>
+        <v>4795.3887527568568</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>262</v>
+      </c>
+      <c r="B26">
+        <v>299792458</v>
+      </c>
+      <c r="C26" s="12">
+        <f>B26/B15</f>
+        <v>2.003960280748663E-3</v>
       </c>
       <c r="F26" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="G26" s="3">
         <f>G25-G22</f>
-        <v>2108.2392389040306</v>
+        <v>3600.2955994487475</v>
       </c>
       <c r="J26" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K26" s="3">
         <f>SQRT(B2/C4)*(1-SQRT(2*C3/(C3+C4)))</f>
         <v>2647.9168707577678</v>
       </c>
     </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>264</v>
+      </c>
+      <c r="B27">
+        <f>60*B26</f>
+        <v>17987547480</v>
+      </c>
+      <c r="C27" s="12">
+        <f>B27/B15</f>
+        <v>0.12023761684491979</v>
+      </c>
       <c r="F27" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="G27" s="3">
-        <f>G26+K27</f>
-        <v>2883.7217400237669</v>
+        <f>G26+K27+9200</f>
+        <v>14947.767481447836</v>
       </c>
       <c r="J27" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K27" s="3">
-        <f>K26*SQRT((1-K24)/2)</f>
-        <v>775.48250111973618</v>
+        <f>K25-K26</f>
+        <v>2147.471881999089</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B28">
+        <f>60*B27</f>
+        <v>1079252848800</v>
+      </c>
+      <c r="C28" s="12">
+        <f>B28/B15</f>
+        <v>7.2142570106951869</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B29">
+        <f>24*B28</f>
+        <v>25902068371200</v>
+      </c>
+      <c r="C29" s="12">
+        <f>B29/B15</f>
+        <v>173.1421682566845</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30">
+        <f>365.25*B29</f>
+        <v>9460730472580800</v>
+      </c>
+      <c r="C30" s="12">
+        <f>B30/B15</f>
+        <v>63240.17695575401</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>269</v>
+      </c>
+      <c r="B31">
+        <f>3.26*B30</f>
+        <v>3.0841981340613404E+16</v>
+      </c>
+      <c r="C31" s="12">
+        <f>B31/B15</f>
+        <v>206162.97687575806</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="9">
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="F1:K1"/>
     <mergeCell ref="F18:K18"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="J19:K19"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:D17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBCA16E7-FD7F-FB45-A5AB-C616D211397D}">
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2">
+        <v>19</v>
+      </c>
+      <c r="C2" s="34">
+        <v>35658</v>
+      </c>
+      <c r="D2" s="34">
+        <v>36469</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <f>DATEDIF(C2, D2, "M")</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3">
+        <v>29</v>
+      </c>
+      <c r="C3" s="33">
+        <v>36029</v>
+      </c>
+      <c r="D3" s="33">
+        <v>36623</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <f>DATEDIF(C3, D3, "M")</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B4">
+        <v>47</v>
+      </c>
+      <c r="C4" s="33">
+        <v>577</v>
+      </c>
+      <c r="D4" s="33">
+        <v>1715</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4">
+        <f>DATEDIF(C4, D4, "M")</f>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>349</v>
+      </c>
+      <c r="B5">
+        <v>32</v>
+      </c>
+      <c r="C5" s="33">
+        <v>589</v>
+      </c>
+      <c r="D5" s="33">
+        <v>1423</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f t="shared" ref="F5:F15" si="0">DATEDIF(C5,D5, "M")</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B6">
+        <f>12+19</f>
+        <v>31</v>
+      </c>
+      <c r="C6" s="33">
+        <v>655</v>
+      </c>
+      <c r="D6" s="33">
+        <v>1471</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B7">
+        <v>31</v>
+      </c>
+      <c r="C7" s="33">
+        <v>1037</v>
+      </c>
+      <c r="D7" s="33">
+        <v>1664</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>352</v>
+      </c>
+      <c r="B8">
+        <f>15+46</f>
+        <v>61</v>
+      </c>
+      <c r="C8" s="33">
+        <v>2780</v>
+      </c>
+      <c r="D8" s="33">
+        <v>3370</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>353</v>
+      </c>
+      <c r="B9">
+        <f>14+18</f>
+        <v>32</v>
+      </c>
+      <c r="C9" s="33">
+        <v>3986</v>
+      </c>
+      <c r="D9" s="33">
+        <v>4555</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B10">
+        <v>20</v>
+      </c>
+      <c r="C10" s="33">
+        <v>3807</v>
+      </c>
+      <c r="D10" s="33">
+        <v>4450</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>355</v>
+      </c>
+      <c r="B11">
+        <v>65</v>
+      </c>
+      <c r="C11" s="33">
+        <v>3820</v>
+      </c>
+      <c r="D11" s="33">
+        <v>4914</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>356</v>
+      </c>
+      <c r="B12">
+        <v>33</v>
+      </c>
+      <c r="C12" s="33">
+        <v>4141</v>
+      </c>
+      <c r="D12" s="33">
+        <v>4737</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>357</v>
+      </c>
+      <c r="B13">
+        <v>55</v>
+      </c>
+      <c r="C13" s="33">
+        <v>4354</v>
+      </c>
+      <c r="D13" s="33">
+        <v>5171</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>358</v>
+      </c>
+      <c r="B14">
+        <v>56</v>
+      </c>
+      <c r="C14" s="33">
+        <v>5334</v>
+      </c>
+      <c r="D14" s="33">
+        <v>6230</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>359</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="C15" s="33">
+        <v>7931</v>
+      </c>
+      <c r="D15" s="33">
+        <v>8295</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B16" s="35">
+        <f>SUM(B2:B15)/14</f>
+        <v>37.928571428571431</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="E16" s="14">
+        <f>SUM(E2:E15)/SUM(B2:B15)</f>
+        <v>3.2015065913370999E-2</v>
+      </c>
+      <c r="F16" s="35">
+        <f>SUM(F2:F15)/14</f>
+        <v>23.785714285714285</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <f>SUM(B2:B15)</f>
+        <v>531</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <f>1/10^LOG(256,2)</f>
+        <v>1E-8</v>
+      </c>
+      <c r="C18" s="3">
+        <f>B18*1000000000</f>
+        <v>10</v>
+      </c>
+      <c r="D18" s="33"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3718D1FB-9059-F54C-B6A1-271203181C1D}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38" t="s">
+        <v>364</v>
+      </c>
+      <c r="D1" s="38"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2">
+        <v>9.8064999999999998</v>
+      </c>
+      <c r="C2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2">
+        <v>78180</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B3">
+        <v>3.7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4">
+        <v>1.2250000000000001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4">
+        <f>D2*1000/D3</f>
+        <v>459882.35294117645</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5">
+        <v>0.02</v>
+      </c>
+      <c r="C5" t="s">
+        <v>365</v>
+      </c>
+      <c r="D5">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D6">
+        <f>D5/7</f>
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D7">
+        <f>D2*B2</f>
+        <v>766672.16999999993</v>
+      </c>
+      <c r="E7" t="s">
+        <v>393</v>
+      </c>
+      <c r="F7">
+        <f>D2*B3</f>
+        <v>289266</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>397</v>
+      </c>
+      <c r="D8">
+        <f>D7</f>
+        <v>766672.16999999993</v>
+      </c>
+      <c r="E8" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8">
+        <f>F7</f>
+        <v>289266</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>398</v>
+      </c>
+      <c r="D9">
+        <f>D7*D6</f>
+        <v>69000.495299999995</v>
+      </c>
+      <c r="E9" t="s">
+        <v>400</v>
+      </c>
+      <c r="F9">
+        <f>1/2*B5*F10^2*D3*D6</f>
+        <v>41323.714285714275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>402</v>
+      </c>
+      <c r="D10">
+        <f>SQRT((2*D2*B2)/(B4*D5*D3))</f>
+        <v>108.10780944151092</v>
+      </c>
+      <c r="E10" t="s">
+        <v>402</v>
+      </c>
+      <c r="F10">
+        <f>SQRT((2*D2*B3)/(B5*D5*D3))</f>
+        <v>519.70148725431</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>401</v>
+      </c>
+      <c r="D11">
+        <f>(D10*3.6)/1.852</f>
+        <v>210.14476997269941</v>
+      </c>
+      <c r="E11" t="s">
+        <v>401</v>
+      </c>
+      <c r="F11">
+        <f>(F10*3.6)/1.852</f>
+        <v>1010.2188737124816</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>403</v>
+      </c>
+      <c r="D12">
+        <f>D9</f>
+        <v>69000.495299999995</v>
+      </c>
+      <c r="E12" t="s">
+        <v>405</v>
+      </c>
+      <c r="F12">
+        <f>F9/1000</f>
+        <v>41.323714285714274</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>404</v>
+      </c>
+      <c r="F13">
+        <f>F8/1000</f>
+        <v>289.26600000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>406</v>
+      </c>
+      <c r="F14">
+        <f>(F12/F13)*100</f>
+        <v>14.285714285714283</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F0FA8B-2D8F-4955-BFE7-B279DB49F0BC}">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="32"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+        <v>89</v>
+      </c>
+      <c r="E1" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="38"/>
+      <c r="I1" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="J1" s="42"/>
+      <c r="K1" s="42"/>
+      <c r="L1" s="42"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B2">
         <v>450</v>
@@ -2086,22 +3494,36 @@
         <v>120100000</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F2">
         <v>27.65</v>
       </c>
       <c r="G2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="H2">
         <f>F2/H3</f>
         <v>537.94185010815625</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I2" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38" t="s">
+        <v>288</v>
+      </c>
+      <c r="P2" s="38"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3">
         <v>311</v>
@@ -2110,22 +3532,49 @@
         <v>43100000</v>
       </c>
       <c r="E3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F3">
         <v>78.59</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H3">
         <f>(F3*1000)/(F5*1000)</f>
         <v>5.1399607586657944E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I3" t="s">
+        <v>297</v>
+      </c>
+      <c r="J3">
+        <v>24</v>
+      </c>
+      <c r="K3" t="s">
+        <v>289</v>
+      </c>
+      <c r="L3">
+        <f>0.00000000001016 * (J5^3) - 0.00000001458 * (J5^2) - 0.00007543 *J5 + 1.423</f>
+        <v>1.40030953725952</v>
+      </c>
+      <c r="M3" t="s">
+        <v>301</v>
+      </c>
+      <c r="N3">
+        <f>840.34+9.241*SQRT(J9)</f>
+        <v>1167.4700947714075</v>
+      </c>
+      <c r="O3" t="s">
+        <v>311</v>
+      </c>
+      <c r="P3">
+        <f>SQRT(N10*N11*287.05)</f>
+        <v>560.3594439034847</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B4">
         <v>350</v>
@@ -2134,184 +3583,465 @@
         <v>50000000</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F4">
         <v>333</v>
       </c>
       <c r="G4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H4">
         <f>F5*(EXP(F2/F6)-1)</f>
         <v>13.001224836801757</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I4" t="s">
+        <v>279</v>
+      </c>
+      <c r="J4">
+        <v>101325</v>
+      </c>
+      <c r="K4" t="s">
+        <v>292</v>
+      </c>
+      <c r="L4">
+        <f>J5*(J7^((L3-1)/L3))</f>
+        <v>527.38933575862188</v>
+      </c>
+      <c r="M4" t="s">
+        <v>291</v>
+      </c>
+      <c r="N4">
+        <f>J9-L13/(N3*J3)</f>
+        <v>1001.7978943849349</v>
+      </c>
+      <c r="O4" t="s">
+        <v>312</v>
+      </c>
+      <c r="P4">
+        <f>J3/(N12*P3*N13)</f>
+        <v>7.146895038451187E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5">
         <v>333</v>
       </c>
-      <c r="C5" t="s">
-        <v>116</v>
-      </c>
       <c r="E5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F5">
         <v>1529</v>
       </c>
       <c r="G5" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H5">
         <f>H4/(F5+H4)</f>
         <v>8.4313972177147561E-3</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I5" t="s">
+        <v>280</v>
+      </c>
+      <c r="J5">
+        <v>288</v>
+      </c>
+      <c r="K5" t="s">
+        <v>291</v>
+      </c>
+      <c r="L5">
+        <f>J5+(L4-J5)/J8</f>
+        <v>579.9382143397828</v>
+      </c>
+      <c r="M5" t="s">
+        <v>292</v>
+      </c>
+      <c r="N5">
+        <f>J9-(J9-N4)/J12</f>
+        <v>957.44164045286459</v>
+      </c>
+      <c r="O5" t="s">
+        <v>106</v>
+      </c>
+      <c r="P5">
+        <f>J3*P3*N13+(N9-J4)*P4</f>
+        <v>16196.469521640649</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="E6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F6">
         <f>F4*9.8065</f>
         <v>3265.5645</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E7" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="F7" s="33"/>
-      <c r="G7" s="33"/>
-      <c r="H7" s="33"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E8" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="32"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I6" t="s">
+        <v>281</v>
+      </c>
+      <c r="J6">
+        <v>0.02</v>
+      </c>
+      <c r="K6" t="s">
+        <v>293</v>
+      </c>
+      <c r="L6">
+        <f>J4*(1-J6)*J7</f>
+        <v>824177.55</v>
+      </c>
+      <c r="M6" t="s">
+        <v>293</v>
+      </c>
+      <c r="N6">
+        <f>L11/(((J9/N5)^(L12/(L12-1))))*(1-J13)</f>
+        <v>264576.43521766545</v>
+      </c>
+      <c r="O6" t="s">
+        <v>314</v>
+      </c>
+      <c r="P6">
+        <f>L10/(P5/1000)</f>
+        <v>3.5317949327713448E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="E7" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="F7" s="39"/>
+      <c r="G7" s="39"/>
+      <c r="H7" s="39"/>
+      <c r="I7" t="s">
+        <v>282</v>
+      </c>
+      <c r="J7">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="K7" t="s">
+        <v>294</v>
+      </c>
+      <c r="L7">
+        <f>830.34+9.241*SQRT(L5)</f>
+        <v>1052.8808967510365</v>
+      </c>
+      <c r="M7" t="s">
+        <v>304</v>
+      </c>
+      <c r="N7">
+        <f>N6/J4</f>
+        <v>2.6111663974109591</v>
+      </c>
+      <c r="O7" t="s">
+        <v>88</v>
+      </c>
+      <c r="P7">
+        <f>L13/L9</f>
+        <v>0.28565802341607893</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="38"/>
+      <c r="I8" t="s">
+        <v>283</v>
+      </c>
+      <c r="J8">
+        <v>0.82</v>
+      </c>
+      <c r="K8" t="s">
+        <v>302</v>
+      </c>
+      <c r="L8">
+        <f>848.34+9.241*SQRT(J5)</f>
+        <v>1005.1649703586772</v>
+      </c>
+      <c r="M8" t="s">
+        <v>305</v>
+      </c>
+      <c r="N8" s="12">
+        <f>MIN(N7,1.8929)</f>
+        <v>1.8929</v>
+      </c>
+      <c r="O8" t="s">
+        <v>313</v>
+      </c>
+      <c r="P8">
+        <f>L10*3600</f>
+        <v>2059.2939234713745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>273</v>
+      </c>
+      <c r="B9">
+        <v>1000</v>
+      </c>
+      <c r="C9" s="5">
+        <v>300000000</v>
+      </c>
       <c r="E9" s="15" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F9" s="4">
         <v>7.88</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H9" s="3">
         <f>(F13*F11)/1000</f>
         <v>78.593900055000006</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>284</v>
+      </c>
+      <c r="J9">
+        <f>980+273.15</f>
+        <v>1253.1500000000001</v>
+      </c>
+      <c r="K9" t="s">
+        <v>295</v>
+      </c>
+      <c r="L9">
+        <f>(L7*(J9-L5)*J3)/0.69</f>
+        <v>24654324.472671177</v>
+      </c>
+      <c r="M9" t="s">
+        <v>309</v>
+      </c>
+      <c r="N9">
+        <f>N6/N8</f>
+        <v>139773.06525313828</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="3">
+        <v>250000</v>
+      </c>
+      <c r="C10">
+        <v>0.1</v>
+      </c>
       <c r="E10" s="15" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F10" s="4">
         <v>17.89</v>
       </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="H10" s="3">
         <f>(F9*C3)/1000000</f>
         <v>339.62799999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>299</v>
+      </c>
+      <c r="J10">
+        <v>0.02</v>
+      </c>
+      <c r="K10" t="s">
+        <v>296</v>
+      </c>
+      <c r="L10" s="12">
+        <f>L9/C3</f>
+        <v>0.57202608985315961</v>
+      </c>
+      <c r="M10" t="s">
+        <v>306</v>
+      </c>
+      <c r="N10">
+        <f>0.00000000001016 * (N5^3) - 0.00000001458 * (N5^2) - 0.00007543 *N5 + 1.423</f>
+        <v>1.3463320151719993</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>270</v>
+      </c>
+      <c r="B11" s="2">
+        <f>(1/SQRT(1-B10^2/C9^2)-1)*B9*C9^2</f>
+        <v>31250016274686.488</v>
+      </c>
+      <c r="C11" s="2">
+        <f>B9*(B10^2)/2</f>
+        <v>31250000000000</v>
+      </c>
       <c r="E11" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F11">
         <f>SUM(F9:F10)</f>
         <v>25.77</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="H11" s="3">
         <f>((F11*F13^2)/2)/1000000</f>
         <v>119.84868307829508</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>285</v>
+      </c>
+      <c r="J11">
+        <v>0.05</v>
+      </c>
+      <c r="K11" t="s">
+        <v>298</v>
+      </c>
+      <c r="L11">
+        <f>L6*(1-J10)</f>
+        <v>807693.99900000007</v>
+      </c>
+      <c r="M11" t="s">
+        <v>307</v>
+      </c>
+      <c r="N11">
+        <f>N5/(N8^((N10-1)/N10))</f>
+        <v>812.50055592616468</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B12" s="3">
+        <f>B11/4184000000000000</f>
+        <v>7.4689331440455278E-3</v>
+      </c>
+      <c r="C12" s="3">
+        <f>C11/B11</f>
+        <v>0.99999947921030363</v>
+      </c>
       <c r="E12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F12">
         <f>B3</f>
         <v>311</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H12" s="14">
         <f>H11/H10</f>
         <v>0.35288222136659841</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>286</v>
+      </c>
+      <c r="J12">
+        <v>0.85</v>
+      </c>
+      <c r="K12" t="s">
+        <v>300</v>
+      </c>
+      <c r="L12">
+        <f>0.00000000001016 * (J9^3) - 0.00000001458 * (J9^2) - 0.00007543 *J9 + 1.423</f>
+        <v>1.3255728304447598</v>
+      </c>
+      <c r="M12" t="s">
+        <v>308</v>
+      </c>
+      <c r="N12">
+        <f>N9/(287.06*N11)</f>
+        <v>0.59927635441798499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>29</v>
+        <v>272</v>
       </c>
       <c r="F13">
         <f>F12*9.8065</f>
         <v>3049.8215</v>
       </c>
       <c r="G13" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H13" s="3">
         <f>H11*1000/(H9*1000)</f>
         <v>1.5249107499999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="E14" s="34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I13" t="s">
+        <v>287</v>
+      </c>
+      <c r="J13">
+        <v>0.02</v>
+      </c>
+      <c r="K13" t="s">
+        <v>303</v>
+      </c>
+      <c r="L13">
+        <f>L8*(L5-J5)*J3</f>
+        <v>7042705.5975219104</v>
+      </c>
+      <c r="M13" t="s">
+        <v>310</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="E14" s="40" t="s">
+        <v>214</v>
+      </c>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="40"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E15" s="32" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="H15" s="32"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="E15" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="38"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B16">
-        <v>3280</v>
+        <v>4800</v>
       </c>
       <c r="C16">
         <v>0.64</v>
@@ -2320,26 +4050,35 @@
         <v>9.1999999999999998E-2</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F16" s="18">
         <f>F17/(F18*9.8065)</f>
-        <v>5.5065517768826795E-2</v>
+        <v>7.9666547697955438E-7</v>
       </c>
       <c r="G16" s="15" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="H16" s="17">
         <f>(H17/F19)</f>
-        <v>2407050</v>
+        <v>1.4959067796610168</v>
       </c>
       <c r="I16" t="s">
+        <v>222</v>
+      </c>
+      <c r="J16" t="s">
+        <v>254</v>
+      </c>
+      <c r="K16" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="L16" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="B17">
         <v>5000</v>
@@ -2351,27 +4090,26 @@
         <v>5</v>
       </c>
       <c r="E17" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F17" s="12">
-        <f>D18</f>
-        <v>16200</v>
+        <v>3.7499999999999999E-2</v>
       </c>
       <c r="G17" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="H17" s="12">
         <f>((F16*(F18*9.8065)^2)/2)/1000</f>
-        <v>2382979.5</v>
+        <v>0.88258499999999984</v>
       </c>
       <c r="I17">
         <f>H17/1000</f>
-        <v>2382.9794999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+        <v>8.8258499999999986E-4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
       <c r="B18">
         <v>30000</v>
@@ -2383,144 +4121,219 @@
         <v>16200</v>
       </c>
       <c r="E18" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F18" s="3">
-        <f>B18</f>
-        <v>30000</v>
+        <v>4800</v>
       </c>
       <c r="G18" s="15" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="H18" s="17">
         <f>H16*(1-F19)</f>
-        <v>24070.500000000022</v>
+        <v>0.61332177966101697</v>
       </c>
       <c r="I18">
         <f>H18/1000</f>
-        <v>24.07050000000002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <v>6.1332177966101696E-4</v>
+      </c>
+      <c r="J18">
+        <f>I18/J26</f>
+        <v>1.4859697891186669E-3</v>
+      </c>
+      <c r="K18">
+        <f>SQRT(J18)</f>
+        <v>3.8548278679062534E-2</v>
+      </c>
+      <c r="L18">
+        <f>SQRT(J18/PI())</f>
+        <v>2.174853729442314E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C19" s="7"/>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F19" s="3">
-        <f>C18</f>
-        <v>0.99</v>
+        <v>0.59</v>
       </c>
       <c r="G19" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="H19" s="12">
         <f>H16/F17</f>
-        <v>148.58333333333334</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+        <v>39.890847457627117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>36000</v>
+        <v>10</v>
       </c>
       <c r="G20" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H20">
         <f>H16/F21</f>
-        <v>66.862499999999997</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0.14959067796610168</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>412</v>
+      </c>
+      <c r="B21">
+        <f>(B4*9.8065)*LN(1500/250)</f>
+        <v>6149.8112322447223</v>
+      </c>
       <c r="E21" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F21" s="3">
-        <v>36000</v>
+        <v>10</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H21" s="2">
         <f>F17/F26</f>
-        <v>0.10030959752321982</v>
-      </c>
-      <c r="I21" s="2">
-        <f>H21*600</f>
-        <v>60.185758513931887</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="I21" s="2"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B22" s="5"/>
       <c r="E22" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F22" s="3">
-        <v>36000</v>
+        <v>10</v>
       </c>
       <c r="G22" s="15" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="H22" s="16">
         <f>F18*9.8065*LN(F26/F24)</f>
-        <v>33741.766776894801</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+        <v>10503.634732621431</v>
+      </c>
+      <c r="I22" s="41" t="s">
+        <v>278</v>
+      </c>
+      <c r="J22" s="41"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E23" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="F23" s="3">
-        <v>36000</v>
+        <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="H23">
         <f>F25/F26</f>
-        <v>0.10835913312693499</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <v>0.2</v>
+      </c>
+      <c r="I23" t="s">
+        <v>257</v>
+      </c>
+      <c r="J23" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F24" s="3">
         <f>SUM(F20:F23)</f>
-        <v>144000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+      <c r="G24" t="s">
+        <v>255</v>
+      </c>
+      <c r="H24">
+        <f>1370+273</f>
+        <v>1643</v>
+      </c>
+      <c r="I24" s="6">
+        <f>H26*(H24^4)</f>
+        <v>413201.05541557289</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3">
-        <v>17500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>256</v>
+      </c>
+      <c r="H25">
+        <v>300</v>
+      </c>
+      <c r="I25" s="6">
+        <f>H26*(H25^4)</f>
+        <v>459.29972699999996</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="F26" s="3">
         <f>F24+F25</f>
-        <v>161500</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+      <c r="G26" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="2">
+        <v>5.6703669999999997E-8</v>
+      </c>
+      <c r="I26" s="6">
+        <f>I24-I25</f>
+        <v>412741.75568857288</v>
+      </c>
+      <c r="J26">
+        <f>I26/1000000</f>
+        <v>0.41274175568857291</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F27">
         <f>F18*9.8065</f>
-        <v>294195</v>
+        <v>47071.199999999997</v>
       </c>
       <c r="H27" s="5"/>
     </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C30">
+        <f>((((4000000*(9200^2))/2)/0.333)/4184000000000)</f>
+        <v>121.49817121136432</v>
+      </c>
+      <c r="D30">
+        <f>800*0.15</f>
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="14">
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="A8:B8"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="G15:H15"/>
@@ -2534,7 +4347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6240741-2D2C-A547-AC9F-188D1B6CC064}">
   <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -2548,466 +4361,473 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="37" t="s">
-        <v>227</v>
-      </c>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="B2">
         <v>273.14999999999998</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F2" s="1"/>
+      <c r="G2" t="s">
+        <v>253</v>
+      </c>
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>175</v>
+        <v>159</v>
       </c>
       <c r="B3" s="2">
         <v>5.6703669999999997E-8</v>
       </c>
       <c r="C3" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="D3">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="F3" s="6">
         <f>B3*D3^4</f>
-        <v>931.41510126318826</v>
+        <v>1121.3372241210936</v>
+      </c>
+      <c r="G3">
+        <f>F3/1000</f>
+        <v>1.1213372241210937</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B4" s="22">
+        <v>167</v>
+      </c>
+      <c r="B4" s="21">
         <v>2.897771955E-3</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>178</v>
+        <v>162</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>273</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="F4" s="6">
         <f>B3*D4^4</f>
-        <v>0.14516139519999999</v>
+        <v>314.96460866335644</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
-        <v>186</v>
-      </c>
-      <c r="B5" s="25">
+      <c r="A5" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="24">
         <v>5780</v>
       </c>
       <c r="C5" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="D5">
         <f>D3-B2</f>
-        <v>84.850000000000023</v>
+        <v>101.85000000000002</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>165</v>
       </c>
       <c r="F5" s="6">
         <f>F3-F4</f>
-        <v>931.26993986798823</v>
+        <v>806.3726154577372</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="25">
+      <c r="A6" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="24">
         <v>255</v>
       </c>
       <c r="C6" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="D6">
         <f>D4-B2</f>
-        <v>-233.14999999999998</v>
+        <v>-0.14999999999997726</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="F6" s="6">
         <f>(B4/D3)*1000000000</f>
-        <v>8094.335069832402</v>
+        <v>7727.3918800000001</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A7" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="B7" s="27">
+      <c r="A7" s="24" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" s="26">
         <v>695000000</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="35"/>
-      <c r="G7" s="35"/>
+      <c r="C7" s="43" t="s">
+        <v>207</v>
+      </c>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="43"/>
     </row>
     <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="B8" s="27">
+      <c r="A8" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="26">
         <v>6370000</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="36"/>
+      <c r="C8" s="44" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="44"/>
       <c r="E8" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="H8" s="24"/>
+        <v>209</v>
+      </c>
+      <c r="H8" s="23"/>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="B9" s="27">
+      <c r="A9" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B9" s="26">
         <v>147000000000</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="C9" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="D9" s="27">
         <v>700</v>
       </c>
-      <c r="E9" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="26">
+      <c r="E9" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F9" s="25">
         <f>POWER(SUM(F24:F27)/F28,0.25)</f>
         <v>284.49041730521611</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="25">
         <f>F9-B2</f>
         <v>11.340417305216135</v>
       </c>
-      <c r="H9" s="23"/>
+      <c r="H9" s="22"/>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="27">
+      <c r="A10" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="26">
         <v>5.6699999999999998E-8</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="27">
+      <c r="C10" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="D10" s="26">
         <f>D9*1000</f>
         <v>700000</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="F10" s="26">
+      <c r="E10" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="F10" s="25">
         <f>POWER(SUM(F26:F28)/F28,0.25)</f>
         <v>232.5501794269895</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="25">
         <f>F10-B2</f>
         <v>-40.599820573010476</v>
       </c>
-      <c r="H10" s="23"/>
+      <c r="H10" s="22"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="B11" s="26">
+      <c r="A11" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B11" s="25">
         <v>0.34</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="D11" s="25">
+      <c r="C11" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="24">
         <v>0.6</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="C12" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="25">
+      <c r="C12" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12" s="24">
         <v>0.9</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="C13" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" s="25">
+      <c r="C13" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D13" s="24">
         <v>700</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="C14" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" s="38"/>
-      <c r="E14" s="29" t="s">
-        <v>212</v>
+      <c r="C14" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="46"/>
+      <c r="E14" s="28" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="C15" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="D15" s="25">
+      <c r="C15" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="24">
         <v>1</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A16" s="25"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="D16" s="25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="24" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="24">
         <v>1</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="24">
         <v>0.8</v>
       </c>
     </row>
     <row r="17" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C17" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="25">
+      <c r="C17" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="D17" s="24">
         <v>4</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="24">
         <v>0.2</v>
       </c>
-      <c r="G17" s="29"/>
+      <c r="G17" s="28"/>
     </row>
     <row r="18" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C18" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="D18" s="38"/>
+      <c r="C18" s="46" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="46"/>
     </row>
     <row r="19" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C19" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="D19" s="25">
+      <c r="C19" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="D19" s="24">
         <f>D16*E16+D17*E17</f>
         <v>1.6</v>
       </c>
     </row>
     <row r="20" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C20" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="D20" s="25">
+      <c r="C20" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="D20" s="24">
         <f>D16*E16+D17*E17</f>
         <v>1.6</v>
       </c>
-      <c r="E20" s="25"/>
-      <c r="F20" s="26"/>
-      <c r="G20" s="26"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C21" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="D21" s="25">
+      <c r="C21" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="D21" s="24">
         <f>D15*E15</f>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C22" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="D22" s="25">
+      <c r="C22" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="D22" s="24">
         <v>6</v>
       </c>
     </row>
     <row r="23" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C23" s="36" t="s">
-        <v>185</v>
-      </c>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
+      <c r="C23" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D23" s="44"/>
+      <c r="E23" s="44"/>
+      <c r="F23" s="44"/>
     </row>
     <row r="24" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C24" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="27">
+      <c r="C24" s="24" t="s">
+        <v>171</v>
+      </c>
+      <c r="D24" s="26">
         <f>4*PI()*POWER(B7,2)*B10*POWER(B5,4)</f>
         <v>3.8412616089382957E+26</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F24" s="26">
+      <c r="E24" s="24" t="s">
+        <v>172</v>
+      </c>
+      <c r="F24" s="25">
         <f>D21*D11*D26</f>
         <v>848.75159346335806</v>
       </c>
     </row>
     <row r="25" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C25" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="D25" s="27">
+      <c r="C25" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="26">
         <f>4*PI()*POWER(B8,2)*B10*POWER(B6,4)</f>
         <v>1.222453953230281E+17</v>
       </c>
-      <c r="E25" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="F25" s="26">
+      <c r="E25" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="25">
         <f>D19*D11*D29</f>
         <v>261.40804780142565</v>
       </c>
     </row>
     <row r="26" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C26" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="26">
+      <c r="C26" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="D26" s="25">
         <f>D24/(4*PI()*POWER(B9,2))</f>
         <v>1414.5859891055968</v>
       </c>
-      <c r="E26" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="F26" s="26">
+      <c r="E26" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="F26" s="25">
         <f>D20*D12*D31</f>
         <v>195.45452269146966</v>
       </c>
     </row>
     <row r="27" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C27" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="D27" s="27">
+      <c r="C27" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="D27" s="26">
         <f>D26*PI()*POWER(B8,2)*B11</f>
         <v>6.1310803347109584E+16</v>
       </c>
-      <c r="E27" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="F27" s="25">
+      <c r="E27" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F27" s="24">
         <f>D13</f>
         <v>700</v>
       </c>
     </row>
     <row r="28" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C28" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="D28" s="26">
+      <c r="C28" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="25">
         <f>D27/(PI()*POWER(B8,2))</f>
         <v>480.959236295903</v>
       </c>
-      <c r="E28" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" s="27">
+      <c r="E28" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="F28" s="26">
         <f>D22*D12*B10</f>
         <v>3.0618000000000001E-7</v>
       </c>
     </row>
     <row r="29" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C29" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="D29" s="26">
+      <c r="C29" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="D29" s="25">
         <f>D28*(1-SQRT(1-POWER(B8,2)/POWER(B8+D10,2)))</f>
         <v>272.30004979315174</v>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
     </row>
     <row r="30" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C30" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="D30" s="26">
+      <c r="C30" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="D30" s="25">
         <f>D25/(4*PI()*POWER(B8,2))</f>
         <v>239.74181043749999</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
     </row>
     <row r="31" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C31" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="D31" s="26">
+      <c r="C31" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="25">
         <f>D30*(1-SQRT(1-POWER(B8,2)/POWER(B8+D10,2)))</f>
         <v>135.7323074246317</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
     </row>
     <row r="32" spans="3:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
     </row>
     <row r="33" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="23"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="23"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3023,255 +4843,685 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4699F051-F30B-DF45-8EC8-4E3137FE1EF1}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32" t="s">
+      <c r="B1" s="38"/>
+      <c r="C1" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D1" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="E1" s="38"/>
+      <c r="F1" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G1" s="29"/>
+      <c r="H1" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="I1" s="1"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="5">
+        <v>3.8600000000000001E+26</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="D2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>442</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="H2" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="5">
+        <v>149600000000</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="D3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3">
+        <v>0.15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>443</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="H3" s="30">
+        <f>(B6*H2)/1000000</f>
+        <v>0.24475913983528561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B4" s="38"/>
+      <c r="C4" s="5"/>
+      <c r="D4" t="s">
+        <v>236</v>
+      </c>
+      <c r="E4">
+        <v>0.4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>334</v>
+      </c>
+      <c r="H4" s="30">
+        <f>(B7*H2)/1000000</f>
+        <v>13.811780636425185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>329</v>
+      </c>
+      <c r="B5" s="5">
+        <v>17000000</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5">
+        <v>0.5</v>
+      </c>
+      <c r="F5" t="s">
+        <v>445</v>
+      </c>
+      <c r="G5" t="s">
+        <v>337</v>
+      </c>
+      <c r="H5" s="30">
+        <f>(10*1000000)/1000</f>
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B6" s="3">
+        <f>B5/E8</f>
+        <v>61189.784958821401</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="D6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E6" s="3">
+        <f>B23*B28*E2*E3*E4*E5*B27</f>
+        <v>339.3704806892593</v>
+      </c>
+      <c r="F6" t="s">
+        <v>446</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="H6" s="3">
+        <f>H5*H3</f>
+        <v>2447.5913983528562</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="3">
+        <f>E9*B6</f>
+        <v>3452945.1591062965</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E7" s="3">
+        <f>B24*B28*E2*E3*E4*(1-E5)*B27</f>
+        <v>231.73908832321885</v>
+      </c>
+      <c r="F7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8" s="38"/>
+      <c r="C8" s="5"/>
+      <c r="D8" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="3">
+        <f>B25*B28*E2*E3*E4*E5*B27</f>
+        <v>277.82415008388097</v>
+      </c>
+      <c r="F8" t="s">
+        <v>448</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B9">
+        <v>735000</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="D9" t="s">
+        <v>244</v>
+      </c>
+      <c r="E9" s="6">
+        <f>B25*E3*B27</f>
+        <v>56.430091418526942</v>
+      </c>
+      <c r="F9" t="s">
+        <v>449</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>389</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B10">
+        <f>B9/365.25</f>
+        <v>2012.3203285420946</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E10">
+        <f>(B23+B24)/2</f>
+        <v>606.41712683297749</v>
+      </c>
+      <c r="F10" t="s">
+        <v>450</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H10" s="3">
+        <f>I15*1000/E8</f>
+        <v>1207.1906683505454</v>
+      </c>
+      <c r="I10">
+        <f>(H10*I9)</f>
+        <v>36215.720050516364</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11">
+        <v>240</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="G11" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="H11">
+        <f>(H10*E9)/1000</f>
+        <v>68.121879774613916</v>
+      </c>
+      <c r="I11">
+        <f>(I10*E9)/1000</f>
+        <v>2043.6563932384176</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>381</v>
+      </c>
+      <c r="B12">
+        <v>84</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="D12" t="s">
+        <v>235</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>451</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="H12" s="3">
+        <f>H5*(H10/1000000)</f>
+        <v>12.071906683505453</v>
+      </c>
+      <c r="I12" s="3">
+        <f>H5*(I10/1000000)</f>
+        <v>362.15720050516364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>388</v>
+      </c>
+      <c r="B13">
+        <v>120</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>427</v>
+      </c>
+      <c r="D13" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13">
+        <v>0.2</v>
+      </c>
+      <c r="F13" t="s">
+        <v>452</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H13" s="3">
+        <f>I12+H6</f>
+        <v>2809.7485988580197</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>378</v>
+      </c>
+      <c r="B14">
+        <v>75</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="D14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E14">
+        <v>0.99</v>
+      </c>
+      <c r="F14" t="s">
+        <v>453</v>
+      </c>
+      <c r="I14">
+        <f t="shared" ref="I14:I20" si="0">B9/6</f>
+        <v>122500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>379</v>
+      </c>
+      <c r="B15">
+        <v>100</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="D15" t="s">
+        <v>239</v>
+      </c>
+      <c r="E15">
+        <v>0.5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>454</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="I15">
+        <f t="shared" si="0"/>
+        <v>335.38672142368245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32" t="s">
+      <c r="B16" s="47"/>
+      <c r="C16" s="5"/>
+      <c r="D16" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="6">
+        <f>B23*B28*E12*E13*E14*E15</f>
+        <v>1756.3882388600503</v>
+      </c>
+      <c r="F16" t="s">
+        <v>455</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.38</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="D17" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="6">
+        <f>B24*B28*E12*E13*E14*E15</f>
+        <v>1199.349479036566</v>
+      </c>
+      <c r="F17" t="s">
+        <v>456</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1.67</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="D18" t="s">
         <v>243</v>
       </c>
-      <c r="F1" s="32"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" s="5">
-        <v>398600000000000</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3">
-        <v>28.05</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E18" s="6">
+        <f>B25*B28*E12*E13*E14*E15</f>
+        <v>1437.8595</v>
+      </c>
+      <c r="F18" t="s">
+        <v>457</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" s="5">
+        <f>B3*B17</f>
+        <v>206447999999.99997</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="D19" t="s">
         <v>244</v>
       </c>
-      <c r="F2">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="5">
-        <v>1.08E-3</v>
-      </c>
-      <c r="C3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F3">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4">
-        <v>6378137</v>
-      </c>
-      <c r="C4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="3">
+      <c r="E19" s="6">
+        <f>B25*E13</f>
+        <v>118</v>
+      </c>
+      <c r="F19" t="s">
+        <v>458</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="5">
+        <f>B18*B3</f>
+        <v>249832000000</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>16.666666666666668</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" s="5">
+        <f>B19^2*4*PI()</f>
+        <v>5.355884759343095E+23</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>231</v>
+      </c>
+      <c r="B22" s="5">
+        <f>B20^2*4*PI()</f>
+        <v>7.8434294293908634E+23</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="D22" t="s">
+        <v>339</v>
+      </c>
+      <c r="E22" s="3">
+        <v>2</v>
+      </c>
+      <c r="F22" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>226</v>
+      </c>
+      <c r="B23" s="6">
+        <f>B2/B21</f>
+        <v>720.70258667653513</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="D23" t="s">
+        <v>335</v>
+      </c>
+      <c r="E23" s="3">
+        <f>E22*24</f>
+        <v>48</v>
+      </c>
+      <c r="F23" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" s="6">
+        <f>B2/B22</f>
+        <v>492.1316669894199</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="D24" t="s">
+        <v>336</v>
+      </c>
+      <c r="E24" s="6">
+        <f>(E23*1000)/B5</f>
+        <v>2.8235294117647061E-3</v>
+      </c>
+      <c r="F24" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>242</v>
+      </c>
+      <c r="B25" s="3">
+        <v>590</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="D25" t="s">
+        <v>338</v>
+      </c>
+      <c r="E25">
         <v>500</v>
       </c>
-      <c r="E4" t="s">
-        <v>247</v>
-      </c>
-      <c r="F4">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B5">
-        <v>23.45</v>
-      </c>
-      <c r="C5" t="s">
-        <v>239</v>
-      </c>
-      <c r="D5" s="3">
-        <f>B4+D4*1000</f>
-        <v>6878137</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B6">
-        <f>180/PI()</f>
-        <v>57.295779513082323</v>
-      </c>
-      <c r="C6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>246</v>
-      </c>
-      <c r="F6" s="31">
-        <f>ASIN(F2*SIN(RADIANS(D2))-F3*COS(RADIANS(B5))*SIN(RADIANS(D2))+F4*SIN(RADIANS(B5))*COS(RADIANS(D2)))</f>
-        <v>0.85065121198789173</v>
-      </c>
-      <c r="G6">
-        <f>F6*B6</f>
-        <v>48.738724284594497</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="3">
-        <f>D5*(1-D3)</f>
-        <v>6878137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D8" s="11">
-        <f>2*PI()/(365.25*86400)</f>
-        <v>1.991021277657232E-7</v>
-      </c>
-      <c r="E8" t="s">
-        <v>249</v>
-      </c>
-      <c r="F8">
-        <f>ASIN(SQRT(1/COS(F6)^2)*((B4/(B4+D5))^2)-SIN(F6)^2)</f>
-        <v>-0.2157153030347479</v>
-      </c>
-      <c r="G8">
-        <f>F8*B6</f>
-        <v>-12.359576440276653</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C9" t="s">
+      <c r="F25" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>232</v>
+      </c>
+      <c r="B26" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>233</v>
+      </c>
+      <c r="B27" s="6">
+        <f>EXP(-B26)</f>
+        <v>0.63762815162177333</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="5">
-        <f>-3/2*B3*(B4/D7)^2*SQRT(B2/D7^3)*COS(RADIANS(D2))</f>
-        <v>-1.36068210211513E-6</v>
-      </c>
-      <c r="E9" t="s">
-        <v>250</v>
-      </c>
-      <c r="F9">
-        <f>2*(PI()-ABS(F8))</f>
-        <v>5.8517547011100906</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C10" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="D10" s="32"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C11" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="30">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C12" s="30" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="30">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C13" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="30">
-        <v>1400</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C14" s="30" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C15" s="30" t="s">
-        <v>231</v>
-      </c>
-      <c r="D15" s="30">
-        <f>D14*D13*D12</f>
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C16" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="D16" s="30">
-        <f>D15*24</f>
-        <v>5040</v>
-      </c>
-    </row>
-    <row r="17" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C17" s="30" t="s">
-        <v>233</v>
-      </c>
-      <c r="D17" s="30"/>
+      <c r="B28" s="30">
+        <f>24+37/60</f>
+        <v>24.616666666666667</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="J30" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:D1"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D11:E11"/>
   </mergeCells>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6850C7A2-4934-144F-9E57-D368FF772F19}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3281,26 +5531,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>9.8064999999999998</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D2">
         <v>1.8</v>
@@ -3314,14 +5564,14 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B3">
         <f>0.378*B2</f>
         <v>3.7068569999999998</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -3335,14 +5585,14 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B4">
         <f>0.166*B2</f>
         <v>1.6278790000000001</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <f>B4</f>
@@ -3358,26 +5608,26 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
+      <c r="A6" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B7">
         <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="D7">
         <f>(D3*2*PI())/60</f>
@@ -3394,14 +5644,14 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B8">
         <f>SQRT(B3/B7)</f>
         <v>0.31652065386689116</v>
       </c>
       <c r="C8" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="D8">
         <f>D4/(D7^2)</f>
@@ -3418,14 +5668,14 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B9">
         <f>(B8*60)/(2*PI())</f>
         <v>3.0225495992156741</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D9" s="14">
         <f>1-(D8-D2)/D8</f>
@@ -3442,7 +5692,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D10">
         <f>2*PI()*D8</f>
@@ -3459,7 +5709,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D11">
         <f>(D10*D3)/60</f>
@@ -3485,13 +5735,263 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FFEAEC-FF0D-3447-A58C-B9B74E828479}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38" t="s">
+        <v>321</v>
+      </c>
+      <c r="F1" s="38"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B2">
+        <v>3.7280000000000002</v>
+      </c>
+      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D2">
+        <f>SQRT(B3/B4)</f>
+        <v>3554.6590724159905</v>
+      </c>
+      <c r="E2" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2">
+        <f>751.748</f>
+        <v>751.74800000000005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B3" s="5">
+        <v>42828370000000</v>
+      </c>
+      <c r="C3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D3">
+        <f>SQRT(2*B3/B4)</f>
+        <v>5027.0470698232593</v>
+      </c>
+      <c r="E3" t="s">
+        <v>373</v>
+      </c>
+      <c r="F3">
+        <f>(F2^2)/B2</f>
+        <v>151589.3389227468</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>3389500</v>
+      </c>
+      <c r="C4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D4">
+        <f>D2*B5-B6</f>
+        <v>4180.5375644147571</v>
+      </c>
+      <c r="E4" t="s">
+        <v>374</v>
+      </c>
+      <c r="F4" s="3">
+        <f>(D10^2)/B2</f>
+        <v>606358.5545734592</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>319</v>
+      </c>
+      <c r="B5">
+        <f>9700/7800</f>
+        <v>1.2435897435897436</v>
+      </c>
+      <c r="C5" t="s">
+        <v>323</v>
+      </c>
+      <c r="D5">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6">
+        <v>240</v>
+      </c>
+      <c r="C6" t="s">
+        <v>324</v>
+      </c>
+      <c r="D6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B7">
+        <v>0.02</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7">
+        <f>SUM(D4:D6)</f>
+        <v>4510.5375644147571</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C8" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8">
+        <f>D7*0.66666</f>
+        <v>3006.9949726927421</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C9" t="s">
+        <v>326</v>
+      </c>
+      <c r="D9">
+        <f>D8/4</f>
+        <v>751.74874317318552</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D10">
+        <f>D8/2</f>
+        <v>1503.497486346371</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>368</v>
+      </c>
+      <c r="B12">
+        <f>(2*PI()*B4)/360</f>
+        <v>59157.934996347802</v>
+      </c>
+      <c r="C12" t="s">
+        <v>370</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f>B12</f>
+        <v>59157.934996347802</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B13">
+        <f>(B12*20)/1000</f>
+        <v>1183.1586999269562</v>
+      </c>
+      <c r="D13">
+        <v>15</v>
+      </c>
+      <c r="E13">
+        <f>B12*COS(RADIANS(D13))</f>
+        <v>57142.177242902239</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>371</v>
+      </c>
+      <c r="B14">
+        <f>(30*E15)/1000</f>
+        <v>1254.9293099073152</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <f>B12*COS(RADIANS(D14))</f>
+        <v>51232.274542265681</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D15">
+        <v>45</v>
+      </c>
+      <c r="E15">
+        <f>B12*COS(RADIANS(D15))</f>
+        <v>41830.976996910511</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16">
+        <f>B12*COS(RADIANS(D16))</f>
+        <v>29578.967498173908</v>
+      </c>
+    </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.2">
+      <c r="D17">
+        <v>75</v>
+      </c>
+      <c r="E17">
+        <f>B12*COS(RADIANS(D17))</f>
+        <v>15311.200245991731</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF0382F-337F-7C4A-853A-6E3ED2317EC1}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -3501,45 +6001,45 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B1" s="7"/>
-      <c r="C1" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="32"/>
+      <c r="C1" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="38"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="32"/>
+      <c r="F1" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="38"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2">
         <v>0.05</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>2700</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>0.8</v>
@@ -3549,7 +6049,7 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="F3" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G3">
         <f>D6-E6</f>
@@ -3558,7 +6058,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D4">
         <v>0.8</v>
@@ -3568,7 +6068,7 @@
         <v>0.70000000000000007</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G4">
         <f>G3*B3</f>
@@ -3577,7 +6077,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D5">
         <v>0.6</v>
@@ -3589,7 +6089,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C6" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D6">
         <f>D3*D4*D5</f>
@@ -3602,12 +6102,12 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C8" s="9" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>0.5</v>
@@ -3617,7 +6117,7 @@
         <v>0.45</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G9">
         <f>D11-E11</f>
@@ -3626,7 +6126,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C10" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -3636,7 +6136,7 @@
         <v>0.9</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G10">
         <f>G9*B3</f>
@@ -3645,7 +6145,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C11" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <f>(1/3)*PI()*D9^2*D10</f>
@@ -3658,12 +6158,12 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C13" s="9" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D14">
         <v>0.5</v>
@@ -3673,7 +6173,7 @@
         <v>0.45</v>
       </c>
       <c r="F14" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G14">
         <f>D16-E16</f>
@@ -3682,7 +6182,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -3692,7 +6192,7 @@
         <v>0.9</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G15">
         <f>G14*B3</f>
@@ -3701,7 +6201,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D16">
         <f>PI()*D14^2*D15</f>
@@ -3714,7 +6214,7 @@
     </row>
     <row r="18" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C18" s="9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
@@ -3723,7 +6223,7 @@
     </row>
     <row r="19" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C19" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D19">
         <v>0.5</v>
@@ -3733,7 +6233,7 @@
         <v>0.45</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G19">
         <f>D21-E21</f>
@@ -3742,7 +6242,7 @@
     </row>
     <row r="20" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C20" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -3752,7 +6252,7 @@
         <v>0.9</v>
       </c>
       <c r="F20" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G20">
         <f>G19*B3</f>
@@ -3761,7 +6261,7 @@
     </row>
     <row r="21" spans="3:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D21">
         <f>2/3*PI()*D19^2*D20</f>
@@ -3774,12 +6274,12 @@
     </row>
     <row r="23" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C23" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C24" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -3789,7 +6289,7 @@
         <v>2.95</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G24">
         <f>D28-E28</f>
@@ -3798,7 +6298,7 @@
     </row>
     <row r="25" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C25" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D25">
         <v>8</v>
@@ -3808,7 +6308,7 @@
         <v>8</v>
       </c>
       <c r="F25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G25">
         <f>G24*B3</f>
@@ -3817,7 +6317,7 @@
     </row>
     <row r="26" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C26" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -3829,7 +6329,7 @@
     </row>
     <row r="27" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -3841,7 +6341,7 @@
     </row>
     <row r="28" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D28">
         <f>PI()*D24^2*D25+2/3*PI()*D24^2*D26+2/3*PI()*D24^2*D27</f>
@@ -3854,12 +6354,12 @@
     </row>
     <row r="30" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C30" s="9" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
     </row>
     <row r="31" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C31" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="D31">
         <v>6371000</v>
@@ -3869,7 +6369,7 @@
         <v>6370999.9500000002</v>
       </c>
       <c r="F31" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="G31">
         <f>D32-E32</f>
@@ -3878,7 +6378,7 @@
     </row>
     <row r="32" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C32" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D32">
         <f>4/3*PI()*D31^3</f>
@@ -3889,7 +6389,7 @@
         <v>1.0832068913425303E+21</v>
       </c>
       <c r="F32" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G32">
         <f>G31*B3</f>
@@ -3898,7 +6398,7 @@
     </row>
     <row r="33" spans="3:7" x14ac:dyDescent="0.2">
       <c r="C33" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="D33">
         <f>D32*B3</f>
@@ -3909,7 +6409,7 @@
         <v>2.924658606624832E+24</v>
       </c>
       <c r="F33" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="G33">
         <f>(G31/(4/3*PI()))^(1/3)</f>
@@ -3918,11 +6418,27 @@
     </row>
     <row r="34" spans="3:7" x14ac:dyDescent="0.2">
       <c r="F34" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="G34">
         <f>G33/1000</f>
         <v>18.26005807513743</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C36" s="9" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="37" spans="3:7" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>50</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3934,7 +6450,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41A21110-64B1-2D40-98F3-59BF0BDE1067}">
   <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -3951,12 +6467,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B1" s="19">
         <v>1000</v>
       </c>
-      <c r="D1" s="20">
+      <c r="D1" s="31">
         <f>4/150</f>
         <v>2.6666666666666668E-2</v>
       </c>
@@ -3979,7 +6495,7 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B2" s="19">
         <f>B1</f>
@@ -3998,7 +6514,7 @@
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B4">
         <v>50000</v>
@@ -4025,7 +6541,7 @@
     </row>
     <row r="5" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="B5" s="19">
         <f>B4*(B2+B1)</f>
@@ -4040,13 +6556,13 @@
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="B6">
         <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>160</v>
+        <v>245</v>
       </c>
       <c r="D6">
         <f>25*12</f>
@@ -4055,11 +6571,9 @@
       <c r="J6" s="4"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>159</v>
-      </c>
+      <c r="A7" s="3"/>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>247</v>
       </c>
       <c r="D7">
         <v>17</v>
@@ -4067,7 +6581,7 @@
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="3" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D8">
         <v>7</v>
@@ -4075,7 +6589,7 @@
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="3" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="D9">
         <f>SUM(D7:D8)</f>
@@ -4085,7 +6599,7 @@
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B10" s="5"/>
       <c r="C10" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="D10">
         <f>10/12</f>
@@ -4095,7 +6609,7 @@
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>248</v>
       </c>
       <c r="D11">
         <f>(D6-D9)*D10</f>
@@ -4106,9 +6620,9 @@
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D12">
+        <v>249</v>
+      </c>
+      <c r="D12" s="19">
         <f>D5*3</f>
         <v>12000</v>
       </c>
@@ -4117,9 +6631,9 @@
       <c r="A13" s="5"/>
       <c r="B13" s="5"/>
       <c r="C13" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="D13">
+        <v>153</v>
+      </c>
+      <c r="D13" s="19">
         <f>D12/D11</f>
         <v>52.173913043478258</v>
       </c>
@@ -4140,9 +6654,9 @@
       <c r="A14" s="5"/>
       <c r="B14" s="5"/>
       <c r="C14" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14">
+        <v>156</v>
+      </c>
+      <c r="D14" s="19">
         <f>D13*12</f>
         <v>626.08695652173913</v>
       </c>
@@ -4151,9 +6665,9 @@
       <c r="A15" s="5"/>
       <c r="B15" s="5"/>
       <c r="C15" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="D15">
+        <v>250</v>
+      </c>
+      <c r="D15" s="19">
         <f>D13/12</f>
         <v>4.3478260869565215</v>
       </c>
@@ -4162,7 +6676,7 @@
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D16" s="19">
         <f>D15/30*1000000</f>
@@ -4174,11 +6688,11 @@
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
       <c r="C17" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D17" s="19">
-        <f>D16*7</f>
-        <v>1014492.7536231885</v>
+        <v>155</v>
+      </c>
+      <c r="D17" s="20">
+        <f>D12*1000000/D18</f>
+        <v>11828.571428571428</v>
       </c>
       <c r="E17">
         <f>E16*7</f>
@@ -4186,24 +6700,15 @@
       </c>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C18" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" s="21">
-        <f>D12*1000000/D17</f>
-        <v>11828.571428571428</v>
+      <c r="C18" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="D18" s="32">
+        <f>D16*7</f>
+        <v>1014492.7536231885</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83FFEAEC-FF0D-3447-A58C-B9B74E828479}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>